--- a/excel-data-cleaner/demo_output/cleaned_output.xlsx
+++ b/excel-data-cleaner/demo_output/cleaned_output.xlsx
@@ -5737,7 +5737,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-19 20:44</t>
+          <t>2026-10-20 00:45</t>
         </is>
       </c>
     </row>
